--- a/LLM_Extraction_and_CrossCritique/interactive-table/results/pipeline_comparison_p2_vs_p4.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/results/pipeline_comparison_p2_vs_p4.xlsx
@@ -822,10 +822,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.6999999999999998</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="F2">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -834,10 +834,10 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="J2">
-        <v>0.5555555555555556</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.6</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="F3">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G3">
         <v>0.5</v>
@@ -866,10 +866,10 @@
         <v>0.5</v>
       </c>
       <c r="I3">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="J3">
-        <v>0.4444444444444444</v>
+        <v>0.5925925925925926</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -886,10 +886,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.7333333333333334</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0.8148148148148149</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J4">
         <v>0.6666666666666666</v>
@@ -918,19 +918,19 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F5">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G5">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0.8000000000000002</v>
+        <v>0.4719576719576719</v>
       </c>
       <c r="J5">
         <v>0.4444444444444444</v>
@@ -944,16 +944,16 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F6">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -962,7 +962,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="J6">
         <v>0.5714285714285714</v>
@@ -982,22 +982,22 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.6</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="F7">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H7">
         <v>0.5</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J7">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1008,10 +1008,10 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E8">
         <v>0.4000000000000001</v>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.462962962962963</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="J8">
         <v>0.6666666666666666</v>
@@ -1040,22 +1040,22 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0.8571428571428571</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -1072,25 +1072,25 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E10">
-        <v>0.6</v>
+        <v>0.7714285714285714</v>
       </c>
       <c r="F10">
         <v>0.8571428571428571</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="J10">
         <v>0.7142857142857143</v>
@@ -1104,13 +1104,13 @@
         <v>19</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>0.8333333333333334</v>
@@ -1125,7 +1125,7 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>0.7222222222222222</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1142,22 +1142,22 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F12">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>0.8101851851851851</v>
+      </c>
+      <c r="J12">
         <v>0.875</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="J12">
-        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F13">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G13">
         <v>0.5</v>
@@ -1186,10 +1186,10 @@
         <v>0.5</v>
       </c>
       <c r="I13">
-        <v>0.5</v>
+        <v>0.5047619047619047</v>
       </c>
       <c r="J13">
-        <v>0.5</v>
+        <v>0.5416666666666666</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1206,22 +1206,22 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F14">
+        <v>0.75</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0.7259259259259259</v>
+      </c>
+      <c r="J14">
         <v>0.875</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="J14">
-        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1238,10 +1238,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.5333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F15">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G15">
         <v>0.5</v>
@@ -1250,7 +1250,7 @@
         <v>0.5</v>
       </c>
       <c r="I15">
-        <v>0.5476190476190476</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="J15">
         <v>0.5</v>
@@ -1270,22 +1270,22 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F16">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G16">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0.4296296296296296</v>
       </c>
       <c r="J16">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1296,13 +1296,13 @@
         <v>25</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E17">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="F17">
         <v>0.8333333333333334</v>
@@ -1314,10 +1314,10 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>0.7111111111111111</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J17">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1328,10 +1328,10 @@
         <v>26</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E18">
         <v>0.6</v>
@@ -1346,10 +1346,10 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.6666666666666666</v>
+        <v>0.6148148148148148</v>
       </c>
       <c r="J18">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1360,25 +1360,25 @@
         <v>27</v>
       </c>
       <c r="C19">
-        <v>0.2</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D19">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E19">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F19">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H19">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I19">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="J19">
         <v>0.625</v>
@@ -1392,16 +1392,16 @@
         <v>28</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E20">
-        <v>0.6999999999999998</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F20">
-        <v>0.875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1410,10 +1410,10 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.8000000000000002</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J20">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1424,28 +1424,28 @@
         <v>29</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E21">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F21">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0.5714285714285714</v>
+        <v>0.875</v>
       </c>
       <c r="J21">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1456,28 +1456,28 @@
         <v>30</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E22">
+        <v>0.6999999999999998</v>
+      </c>
+      <c r="F22">
+        <v>0.875</v>
+      </c>
+      <c r="G22">
         <v>0.6</v>
-      </c>
-      <c r="F22">
-        <v>0.75</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
       </c>
       <c r="H22">
         <v>0.75</v>
       </c>
       <c r="I22">
-        <v>0.5714285714285714</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="J22">
-        <v>0.5</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0.6999999999999998</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="F23">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G23">
         <v>0.75</v>
@@ -1506,10 +1506,10 @@
         <v>0.75</v>
       </c>
       <c r="I23">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1526,10 +1526,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.6999999999999998</v>
+        <v>0.7047619047619048</v>
       </c>
       <c r="F24">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1538,10 +1538,10 @@
         <v>1</v>
       </c>
       <c r="I24">
+        <v>0.8412698412698413</v>
+      </c>
+      <c r="J24">
         <v>0.6666666666666666</v>
-      </c>
-      <c r="J24">
-        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1552,28 +1552,28 @@
         <v>33</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F25">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G25">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="H25">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
       <c r="I25">
-        <v>0.7555555555555555</v>
+        <v>0.769047619047619</v>
       </c>
       <c r="J25">
-        <v>0.5</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1584,10 +1584,10 @@
         <v>34</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E26">
         <v>0.6</v>
@@ -1596,16 +1596,16 @@
         <v>0.75</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>0.8000000000000002</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J26">
-        <v>0.5</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1616,16 +1616,16 @@
         <v>35</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F27">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0.5714285714285714</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="J27">
-        <v>0.5</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1654,22 +1654,22 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0.5</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F28">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>0.525925925925926</v>
+      </c>
+      <c r="J28">
         <v>0.625</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0.5</v>
-      </c>
-      <c r="J28">
-        <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1680,16 +1680,16 @@
         <v>37</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>0.5</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F29">
-        <v>0.625</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1698,10 +1698,10 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>0.5714285714285714</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J29">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1712,16 +1712,16 @@
         <v>38</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E30">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F30">
-        <v>0.625</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1730,10 +1730,10 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>0.7222222222222222</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="J30">
-        <v>0.5416666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1744,16 +1744,16 @@
         <v>39</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F31">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1762,10 +1762,10 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>0.5833333333333334</v>
+        <v>0.6</v>
       </c>
       <c r="J31">
-        <v>0.5833333333333334</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1776,28 +1776,28 @@
         <v>40</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F32">
+        <v>0.875</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>0.6222222222222222</v>
+      </c>
+      <c r="J32">
         <v>0.75</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
-      <c r="I32">
-        <v>0.8000000000000002</v>
-      </c>
-      <c r="J32">
-        <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1808,16 +1808,16 @@
         <v>41</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F33">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1826,10 +1826,10 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>0.6666666666666666</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="J33">
-        <v>0.5</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1840,10 +1840,10 @@
         <v>42</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E34">
         <v>0.6</v>
@@ -1858,10 +1858,10 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>0.6031746031746031</v>
+        <v>0.5462962962962963</v>
       </c>
       <c r="J34">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1872,28 +1872,28 @@
         <v>43</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E35">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F35">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>0.6944444444444443</v>
+      </c>
+      <c r="J35">
         <v>0.75</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35">
-        <v>0.5</v>
-      </c>
-      <c r="J35">
-        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1910,22 +1910,22 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0.6</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F36">
         <v>0.75</v>
       </c>
       <c r="G36">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>0.6349206349206349</v>
+        <v>0.75</v>
       </c>
       <c r="J36">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1936,16 +1936,16 @@
         <v>45</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F37">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -1954,10 +1954,10 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>0.5608465608465608</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J37">
-        <v>0.5833333333333334</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -1974,10 +1974,10 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F38">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -1986,10 +1986,10 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0.6666666666666666</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="J38">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2000,28 +2000,28 @@
         <v>47</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F39">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G39">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>0.5046296296296297</v>
+        <v>0.7518518518518519</v>
       </c>
       <c r="J39">
-        <v>0.5416666666666666</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2032,16 +2032,16 @@
         <v>48</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F40">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2050,10 +2050,10 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>0.5714285714285714</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J40">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2064,28 +2064,28 @@
         <v>49</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F41">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="G41">
+        <v>0.5</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="J41">
         <v>0.75</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="J41">
-        <v>0.5</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2096,16 +2096,16 @@
         <v>50</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F42">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2114,10 +2114,10 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J42">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2128,16 +2128,16 @@
         <v>51</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F43">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2146,10 +2146,10 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J43">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2160,16 +2160,16 @@
         <v>52</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>0.5</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="F44">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2178,10 +2178,10 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>0.6666666666666666</v>
+        <v>0.8842592592592592</v>
       </c>
       <c r="J44">
-        <v>0.5</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2192,16 +2192,16 @@
         <v>53</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E45">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F45">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2210,7 +2210,7 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <v>0.5476190476190476</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="J45">
         <v>0.5</v>
@@ -2224,28 +2224,28 @@
         <v>54</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E46">
-        <v>0.7259259259259259</v>
+        <v>0.5</v>
       </c>
       <c r="F46">
-        <v>0.875</v>
+        <v>0.625</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46">
-        <v>0.8000000000000002</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="J46">
-        <v>0.5</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2256,28 +2256,28 @@
         <v>55</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F47">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="J47">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2288,28 +2288,28 @@
         <v>56</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F48">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G48">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>0.611111111111111</v>
+        <v>0.5</v>
       </c>
       <c r="J48">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2320,28 +2320,28 @@
         <v>57</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <v>0.6666666666666666</v>
       </c>
       <c r="F49">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J49">
         <v>0.75</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="J49">
-        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2352,28 +2352,28 @@
         <v>58</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F50">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>0.6031746031746031</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J50">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2390,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F51">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2402,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>0.611111111111111</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="J51">
         <v>0.5</v>
@@ -2416,28 +2416,28 @@
         <v>60</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>0.6666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F52">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J52">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2448,16 +2448,16 @@
         <v>61</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53">
         <v>0.6666666666666666</v>
       </c>
       <c r="F53">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -2466,10 +2466,10 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>0.7777777777777778</v>
+        <v>0.7259259259259259</v>
       </c>
       <c r="J53">
-        <v>0.5833333333333334</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2480,16 +2480,16 @@
         <v>62</v>
       </c>
       <c r="C54">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F54">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2498,10 +2498,10 @@
         <v>0.5</v>
       </c>
       <c r="I54">
-        <v>0.8333333333333334</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="J54">
-        <v>0.625</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2524,16 +2524,16 @@
         <v>0.75</v>
       </c>
       <c r="G55">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="H55">
         <v>0.5</v>
       </c>
       <c r="I55">
-        <v>0.6349206349206349</v>
+        <v>0.6</v>
       </c>
       <c r="J55">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2544,28 +2544,28 @@
         <v>64</v>
       </c>
       <c r="C56">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F56">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H56">
         <v>0.5</v>
       </c>
       <c r="I56">
-        <v>0.7142857142857143</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="J56">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2576,16 +2576,16 @@
         <v>65</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E57">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F57">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2594,10 +2594,10 @@
         <v>0.5</v>
       </c>
       <c r="I57">
-        <v>0.5238095238095238</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="J57">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2626,10 +2626,10 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>0.8000000000000002</v>
+        <v>0.8042328042328042</v>
       </c>
       <c r="J58">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -2646,22 +2646,22 @@
         <v>0</v>
       </c>
       <c r="E59">
+        <v>0.6</v>
+      </c>
+      <c r="F59">
+        <v>0.75</v>
+      </c>
+      <c r="G59">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59">
+        <v>0.6455026455026455</v>
+      </c>
+      <c r="J59">
         <v>0.6666666666666666</v>
-      </c>
-      <c r="F59">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="G59">
-        <v>1</v>
-      </c>
-      <c r="H59">
-        <v>1</v>
-      </c>
-      <c r="I59">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="J59">
-        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -2672,16 +2672,16 @@
         <v>68</v>
       </c>
       <c r="C60">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>0.6</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="F60">
-        <v>0.8571428571428571</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -2690,10 +2690,10 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>0.6944444444444443</v>
+        <v>0.5703703703703704</v>
       </c>
       <c r="J60">
-        <v>0.6666666666666666</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2704,28 +2704,28 @@
         <v>69</v>
       </c>
       <c r="C61">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F61">
-        <v>0.8571428571428571</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61">
-        <v>0.7936507936507936</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="J61">
-        <v>0.7142857142857143</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="F62">
         <v>0.5555555555555556</v>
@@ -2754,10 +2754,10 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>0.5714285714285714</v>
+        <v>0.7936507936507936</v>
       </c>
       <c r="J62">
-        <v>0.4444444444444444</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -2768,13 +2768,13 @@
         <v>71</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>0.6</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="F63">
         <v>0.8571428571428571</v>
@@ -2786,10 +2786,10 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>0.888888888888889</v>
+        <v>0.6203703703703703</v>
       </c>
       <c r="J63">
-        <v>0.7142857142857143</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -2800,13 +2800,13 @@
         <v>72</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>0.6</v>
+        <v>0.8214285714285715</v>
       </c>
       <c r="F64">
         <v>0.8571428571428571</v>
@@ -2838,22 +2838,22 @@
         <v>1</v>
       </c>
       <c r="E65">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F65">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65">
-        <v>0.7222222222222223</v>
+        <v>0.5851851851851851</v>
       </c>
       <c r="J65">
-        <v>0.5833333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -2864,16 +2864,16 @@
         <v>74</v>
       </c>
       <c r="C66">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F66">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G66">
         <v>0.5</v>
@@ -2882,10 +2882,10 @@
         <v>0.5</v>
       </c>
       <c r="I66">
-        <v>0.5238095238095238</v>
+        <v>0.75</v>
       </c>
       <c r="J66">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -2896,10 +2896,10 @@
         <v>75</v>
       </c>
       <c r="C67">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E67">
         <v>0.6</v>
@@ -2908,16 +2908,16 @@
         <v>0.75</v>
       </c>
       <c r="G67">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H67">
         <v>0.5</v>
       </c>
       <c r="I67">
-        <v>0.5714285714285714</v>
+        <v>0.7797619047619048</v>
       </c>
       <c r="J67">
-        <v>0.5</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2928,28 +2928,28 @@
         <v>76</v>
       </c>
       <c r="C68">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>0.6</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F68">
-        <v>0.8571428571428571</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>0.3888888888888888</v>
       </c>
       <c r="H68">
         <v>0.5</v>
       </c>
       <c r="I68">
-        <v>0.8000000000000002</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="J68">
-        <v>0.5714285714285714</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -2960,10 +2960,10 @@
         <v>77</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E69">
         <v>0.5</v>
@@ -2972,16 +2972,16 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G69">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="H69">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="J69">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -2992,28 +2992,28 @@
         <v>78</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E70">
-        <v>0.5</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="F70">
         <v>0.8333333333333334</v>
       </c>
       <c r="G70">
-        <v>0.3333333333333333</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="H70">
-        <v>0.3333333333333333</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="I70">
-        <v>1</v>
+        <v>0.6654761904761904</v>
       </c>
       <c r="J70">
-        <v>0.6666666666666666</v>
+        <v>0.7222222222222222</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -3042,10 +3042,10 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>0.6031746031746031</v>
+        <v>0.5</v>
       </c>
       <c r="J71">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -3056,13 +3056,13 @@
         <v>80</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>0.5</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="F72">
         <v>0.8333333333333334</v>
@@ -3074,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>0.6547619047619048</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="J72">
         <v>0.8333333333333334</v>
@@ -3094,22 +3094,22 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F73">
+        <v>0.875</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73">
+        <v>0.6</v>
+      </c>
+      <c r="J73">
         <v>0.75</v>
-      </c>
-      <c r="G73">
-        <v>1</v>
-      </c>
-      <c r="H73">
-        <v>1</v>
-      </c>
-      <c r="I73">
-        <v>0.6031746031746031</v>
-      </c>
-      <c r="J73">
-        <v>0.5</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3126,10 +3126,10 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F74">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3138,10 +3138,10 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>0.7555555555555555</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="J74">
-        <v>0.5</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3152,16 +3152,16 @@
         <v>83</v>
       </c>
       <c r="C75">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>0.6</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="F75">
-        <v>0.8571428571428571</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -3170,10 +3170,10 @@
         <v>1</v>
       </c>
       <c r="I75">
-        <v>0.625</v>
+        <v>0.4814814814814815</v>
       </c>
       <c r="J75">
-        <v>0.7142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3190,10 +3190,10 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F76">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3202,10 +3202,10 @@
         <v>1</v>
       </c>
       <c r="I76">
-        <v>0.5787037037037037</v>
+        <v>0.6</v>
       </c>
       <c r="J76">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3222,22 +3222,22 @@
         <v>0</v>
       </c>
       <c r="E77">
+        <v>0.6</v>
+      </c>
+      <c r="F77">
+        <v>0.75</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77">
         <v>0.6999999999999998</v>
       </c>
-      <c r="F77">
+      <c r="J77">
         <v>0.875</v>
-      </c>
-      <c r="G77">
-        <v>1</v>
-      </c>
-      <c r="H77">
-        <v>1</v>
-      </c>
-      <c r="I77">
-        <v>0.8095238095238094</v>
-      </c>
-      <c r="J77">
-        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3254,19 +3254,19 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>0.7259259259259259</v>
+        <v>0.6</v>
       </c>
       <c r="F78">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78">
-        <v>0.6666666666666666</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="J78">
         <v>0.5</v>
@@ -3286,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>0.7259259259259259</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F79">
         <v>0.875</v>
@@ -3298,10 +3298,10 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <v>0.5714285714285714</v>
+        <v>0.625</v>
       </c>
       <c r="J79">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -3330,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>0.6666666666666666</v>
+        <v>0.5222222222222223</v>
       </c>
       <c r="J80">
         <v>0.5</v>
@@ -3362,10 +3362,10 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <v>0.6666666666666666</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="J81">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3376,10 +3376,10 @@
         <v>90</v>
       </c>
       <c r="C82">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>0.6999999999999998</v>
@@ -3388,16 +3388,16 @@
         <v>0.875</v>
       </c>
       <c r="G82">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="H82">
         <v>0.5</v>
       </c>
       <c r="I82">
-        <v>1</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="J82">
-        <v>0.625</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3420,16 +3420,16 @@
         <v>0.75</v>
       </c>
       <c r="G83">
-        <v>0.5</v>
+        <v>0.3888888888888888</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
       <c r="I83">
-        <v>0.6527777777777778</v>
+        <v>0.7714285714285714</v>
       </c>
       <c r="J83">
-        <v>0.5833333333333334</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -3446,22 +3446,22 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F84">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G84">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84">
-        <v>0.746031746031746</v>
+        <v>0.625</v>
       </c>
       <c r="J84">
-        <v>0.5833333333333334</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3472,28 +3472,28 @@
         <v>93</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F85">
+        <v>0.875</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J85">
         <v>0.75</v>
-      </c>
-      <c r="G85">
-        <v>1</v>
-      </c>
-      <c r="H85">
-        <v>1</v>
-      </c>
-      <c r="I85">
-        <v>0.5476190476190476</v>
-      </c>
-      <c r="J85">
-        <v>0.5</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3504,28 +3504,28 @@
         <v>94</v>
       </c>
       <c r="C86">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F86">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G86">
-        <v>0.5</v>
+        <v>0.3888888888888888</v>
       </c>
       <c r="H86">
         <v>0.5</v>
       </c>
       <c r="I86">
-        <v>0.625</v>
+        <v>0.6777777777777777</v>
       </c>
       <c r="J86">
-        <v>0.625</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -3542,10 +3542,10 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F87">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -3554,10 +3554,10 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>0.5714285714285714</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="J87">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -3568,16 +3568,16 @@
         <v>96</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F88">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -3586,10 +3586,10 @@
         <v>1</v>
       </c>
       <c r="I88">
-        <v>0.5714285714285714</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J88">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -3606,22 +3606,22 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F89">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G89">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
       <c r="I89">
-        <v>0.6666666666666666</v>
+        <v>0.462962962962963</v>
       </c>
       <c r="J89">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -3638,10 +3638,10 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F90">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -3653,7 +3653,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="J90">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -3682,10 +3682,10 @@
         <v>1</v>
       </c>
       <c r="I91">
-        <v>0.6031746031746031</v>
+        <v>0.5648148148148148</v>
       </c>
       <c r="J91">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3699,22 +3699,22 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D92">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E92">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F92">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G92">
         <v>1</v>
       </c>
       <c r="H92">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I92">
-        <v>0.6845238095238096</v>
+        <v>0.625</v>
       </c>
       <c r="J92">
         <v>0.625</v>
@@ -3740,13 +3740,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="G93">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>1</v>
       </c>
       <c r="I93">
-        <v>0.7555555555555555</v>
+        <v>0.7238095238095239</v>
       </c>
       <c r="J93">
         <v>0.5714285714285714</v>
@@ -3760,28 +3760,28 @@
         <v>102</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E94">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F94">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="G94">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94">
+        <v>0.6444444444444444</v>
+      </c>
+      <c r="J94">
         <v>0.75</v>
-      </c>
-      <c r="G94">
-        <v>0.5</v>
-      </c>
-      <c r="H94">
-        <v>0.5</v>
-      </c>
-      <c r="I94">
-        <v>0.611111111111111</v>
-      </c>
-      <c r="J94">
-        <v>0.5</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -3792,28 +3792,28 @@
         <v>103</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>0.2777777777777777</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E95">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F95">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J95">
-        <v>0.5</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -3824,16 +3824,16 @@
         <v>104</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E96">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F96">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -3842,10 +3842,10 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>0.7222222222222222</v>
+        <v>0.6583333333333333</v>
       </c>
       <c r="J96">
-        <v>0.5416666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -3856,10 +3856,10 @@
         <v>105</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>0.6</v>
@@ -3874,10 +3874,10 @@
         <v>0</v>
       </c>
       <c r="I97">
-        <v>0.8000000000000002</v>
+        <v>0.5423280423280423</v>
       </c>
       <c r="J97">
-        <v>0.5714285714285714</v>
+        <v>0.6190476190476191</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -3888,10 +3888,10 @@
         <v>106</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E98">
         <v>0.6</v>
@@ -3900,16 +3900,16 @@
         <v>0.75</v>
       </c>
       <c r="G98">
-        <v>0.7777777777777777</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="H98">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I98">
-        <v>0.6825396825396824</v>
+        <v>0.5787037037037037</v>
       </c>
       <c r="J98">
-        <v>0.5416666666666666</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -3920,28 +3920,28 @@
         <v>107</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99">
+        <v>0.6999999999999998</v>
+      </c>
+      <c r="F99">
+        <v>0.875</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
         <v>0.6</v>
       </c>
-      <c r="F99">
+      <c r="J99">
         <v>0.75</v>
-      </c>
-      <c r="G99">
-        <v>0</v>
-      </c>
-      <c r="H99">
-        <v>0</v>
-      </c>
-      <c r="I99">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="J99">
-        <v>0.5</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -3952,7 +3952,7 @@
         <v>108</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3964,16 +3964,16 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H100">
         <v>1</v>
       </c>
       <c r="I100">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="J100">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -3984,13 +3984,13 @@
         <v>109</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E101">
-        <v>0.5185185185185185</v>
+        <v>0.5</v>
       </c>
       <c r="F101">
         <v>0.8333333333333334</v>
@@ -4002,10 +4002,10 @@
         <v>1</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J101">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -4131,19 +4131,19 @@
         <v>116</v>
       </c>
       <c r="B2">
-        <v>0.1336666666666667</v>
+        <v>0.355111111111111</v>
       </c>
       <c r="C2">
-        <v>0.7247222222222222</v>
+        <v>0.7461666666666668</v>
       </c>
       <c r="D2">
         <v>4</v>
       </c>
       <c r="E2">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4151,19 +4151,19 @@
         <v>117</v>
       </c>
       <c r="B3">
-        <v>0.1475</v>
+        <v>0.3808333333333334</v>
       </c>
       <c r="C3">
-        <v>0.7308333333333333</v>
+        <v>0.8080555555555555</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4171,19 +4171,19 @@
         <v>118</v>
       </c>
       <c r="B4">
-        <v>0.6144074074074074</v>
+        <v>0.6511865079365079</v>
       </c>
       <c r="C4">
-        <v>0.6912976190476189</v>
+        <v>0.6686468253968253</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E4">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4191,19 +4191,19 @@
         <v>119</v>
       </c>
       <c r="B5">
-        <v>0.7806481481481481</v>
+        <v>0.8038624338624338</v>
       </c>
       <c r="C5">
-        <v>0.5602777777777777</v>
+        <v>0.7089021164021163</v>
       </c>
       <c r="D5">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -4247,16 +4247,16 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E2">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -4267,22 +4267,22 @@
         <v>117</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E3">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4290,22 +4290,22 @@
         <v>118</v>
       </c>
       <c r="B4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="E4">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G4">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4313,22 +4313,22 @@
         <v>119</v>
       </c>
       <c r="B5">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
